--- a/branches/migration/2027.0.0-alpha.6-template-v0.11.1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
+++ b/branches/migration/2027.0.0-alpha.6-template-v0.11.1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T18:44:55+00:00</t>
+    <t>2026-08-25T18:53:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
